--- a/artfynd/A 2368-2024 artfynd.xlsx
+++ b/artfynd/A 2368-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126635827</v>
+        <v>114932700</v>
       </c>
       <c r="B2" t="n">
-        <v>56953</v>
+        <v>97785</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,49 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100038</v>
+        <v>2606</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långakärr, Karlshamn, Bl</t>
+          <t>Långakärr, Bl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493137</v>
+        <v>493037</v>
       </c>
       <c r="R2" t="n">
-        <v>6226381</v>
+        <v>6226284</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,8 +758,19 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Bergbrant mot väster i ädellövskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,10 +780,453 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
+          <t>Johan Wolgast</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>114932735</v>
+      </c>
+      <c r="B3" t="n">
+        <v>96231</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Långakärr, Bl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>493037</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6226284</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Karlshamn</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Asarum</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Bergbrant mot väster i ädellövskog</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Johan Wolgast</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Johan Wolgast</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126635827</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57247</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100038</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogsduva</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Columba oenas</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Långakärr, Karlshamn, Bl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>493137</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6226381</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Karlshamn</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Asarum</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Johan Wolgast</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
           <t>Johan Wolgast, Eva Thulin</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>10119</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56879</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100070</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Sandödla</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lacerta agilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>18D Karlshamn, Bl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>493248</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6226433</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Karlshamn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Asarum</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2004-07-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2004-07-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1 ad F, 1 subad. Obs av Annika Lydänge. Se Inventering av sandödla i Blekinge län 2004. 2005:4 Länsstyrelsen Blekinge</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Blekinge (Anly)</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Via Länsstyrelsen i Blekinge (Anly)</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>111166068</v>
+      </c>
+      <c r="B6" t="n">
+        <v>43258</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>201129</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vitfläckig guldvinge</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycaena virgaureae</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Långakärr, skyttebanan, Bl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>493176</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6226305</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Karlshamn</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Asarum</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-07-30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-07-30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Plan med låga örter som käringtand, höstfibbla och brunört</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Johan Wolgast</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Johan Wolgast, Eva Thulin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2368-2024 artfynd.xlsx
+++ b/artfynd/A 2368-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114932700</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114932735</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126635827</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1111,6 +1131,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/10119</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,8 +1252,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111166068</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>